--- a/AAII_Financials/Quarterly/MONOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MONOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="92">
   <si>
     <t>MONOY</t>
   </si>
@@ -656,78 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,8 +771,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,8 +815,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -849,8 +859,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -866,8 +879,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,8 +921,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,8 +965,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -989,8 +1009,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1030,8 +1053,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,8 +1070,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1085,8 +1112,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,8 +1156,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1143,8 +1176,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1184,8 +1218,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1225,8 +1262,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1266,8 +1306,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1307,8 +1350,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1348,8 +1394,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1389,8 +1438,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1430,8 +1482,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1471,8 +1526,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1512,8 +1570,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1614,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1594,8 +1658,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,8 +1702,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1676,8 +1746,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1717,8 +1790,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1758,8 +1834,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1799,54 +1878,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1862,8 +1947,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1879,49 +1965,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>254300</v>
+      </c>
+      <c r="E41" s="3">
         <v>301600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>248000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>195400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>85800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>85800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>63200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>67400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1961,295 +2051,319 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>308100</v>
+      </c>
+      <c r="E43" s="3">
         <v>330700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>316400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>263400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>243800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>263500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>259900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>237200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>242900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>237200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>242900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>263200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>251700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E44" s="3">
         <v>143100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>155400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>131400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>124800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>125900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>133900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>133600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>144100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>133600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>144100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>148800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>148500</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>8100</v>
       </c>
       <c r="J45" s="3">
         <v>8100</v>
       </c>
       <c r="K45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="L45" s="3">
         <v>8700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>8700</v>
       </c>
       <c r="N45" s="3">
         <v>8700</v>
       </c>
       <c r="O45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="P45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>753900</v>
+      </c>
+      <c r="E46" s="3">
         <v>785200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>731900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>598600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>514900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>493500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>534100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>434700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>481400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>434700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>481400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>483900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E47" s="3">
         <v>38800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>48100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>48100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>333100</v>
+      </c>
+      <c r="E48" s="3">
         <v>350500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>313100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>237300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>240200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>258700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>280700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>257000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>254500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>257000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>254500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>272600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>265800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E49" s="3">
         <v>49000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>54000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>41400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>41700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>45100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>48100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>51100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>48100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>51100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>54200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2289,8 +2403,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2330,16 +2447,19 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2371,8 +2491,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2412,49 +2535,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1175200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1232500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1149400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>922500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>838600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>839900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>910500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>786400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>835100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>786400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>835100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>858000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>847300</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2470,8 +2599,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2487,254 +2617,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E57" s="3">
         <v>159600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>155700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>126100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>116400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>131200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>121000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>109600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>124000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>109600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>138300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>6300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>31900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>36200</v>
       </c>
       <c r="O58" s="3">
         <v>36200</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>110700</v>
+      </c>
+      <c r="E59" s="3">
         <v>173100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>101900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>81300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>66800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>103700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>69400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>79800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>69400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>79800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>78100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>279900</v>
+      </c>
+      <c r="E60" s="3">
         <v>341600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>269300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>231900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>218300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>221800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>262400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>214900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>239300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>214900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>239300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>256600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>239400</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>126100</v>
+      </c>
+      <c r="E61" s="3">
         <v>82900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E62" s="3">
         <v>19600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2774,8 +2923,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2967,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2856,49 +3011,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>429800</v>
+      </c>
+      <c r="E66" s="3">
         <v>448400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>357600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>259300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>246200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>251200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>293500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>240100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>279200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>240100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>279200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>296100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>296600</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,8 +3075,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2955,8 +3117,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2996,8 +3161,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3037,8 +3205,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3078,49 +3249,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>759400</v>
+      </c>
+      <c r="E72" s="3">
         <v>770100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>775700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>645400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>572500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>567600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>592900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>521800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>529900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>521800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>529900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>537300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>524900</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3160,8 +3337,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3201,8 +3381,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3242,49 +3425,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>743100</v>
+      </c>
+      <c r="E76" s="3">
         <v>781400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>787600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>659600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>591200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>586300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>613400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>541700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>550400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>541700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>550400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>559200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3324,54 +3513,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3411,8 +3606,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3428,8 +3626,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3469,8 +3668,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3510,8 +3712,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3756,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3592,8 +3800,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3633,8 +3844,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3674,8 +3888,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3715,8 +3932,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3732,8 +3952,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3773,8 +3994,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3814,8 +4038,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3855,8 +4082,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3896,8 +4126,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3913,8 +4146,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3954,8 +4188,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3995,8 +4232,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4036,8 +4276,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4077,8 +4320,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4118,8 +4364,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4159,8 +4408,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4198,6 +4450,9 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
